--- a/NBA_Finals_Spurs_Knicks_Stats.xlsx
+++ b/NBA_Finals_Spurs_Knicks_Stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adamkaribian/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E2EEB93-8232-294D-9DEF-6A01250676B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EC7EA9C-BCDB-DE44-B5B4-5437B52043B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="360" yWindow="620" windowWidth="28040" windowHeight="16080" activeTab="7" xr2:uid="{7BDB8F1F-88A5-804B-B69B-31264D15A624}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4738" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4496" uniqueCount="263">
   <si>
     <t>Player</t>
   </si>
@@ -835,15 +835,6 @@
   </si>
   <si>
     <t>11-21</t>
-  </si>
-  <si>
-    <t>11-25</t>
-  </si>
-  <si>
-    <t>11-18</t>
-  </si>
-  <si>
-    <t>5-18</t>
   </si>
 </sst>
 </file>
@@ -13806,7 +13797,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F1BDEF0-D7A0-B141-9ABB-88CC0DA9304B}">
-  <dimension ref="A1:O32"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.5" style="4" customWidth="1"/>
@@ -14659,387 +14650,6 @@
         <v>76</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A24" s="7" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A25" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="I25" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J25" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="K25" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="L25" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="M25" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="N25" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="O25" s="4" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A26" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="H26" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="I26" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J26" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="K26" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="L26" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="M26" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="N26" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="O26" s="4" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A27" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="I27" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="J27" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="K27" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="L27" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="M27" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="N27" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="O27" s="4" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A28" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H28" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="I28" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J28" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="K28" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="L28" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="M28" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="N28" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="O28" s="4" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A29" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H29" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="I29" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="J29" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="K29" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="L29" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="M29" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="N29" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="O29" s="4" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A30" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="I30" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="J30" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="K30" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="L30" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="M30" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="N30" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="O30" s="4" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A31" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="H31" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="I31" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="J31" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="K31" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="L31" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="M31" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="N31" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="O31" s="4" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A32" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H32" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="I32" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J32" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="K32" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="L32" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="M32" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="N32" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="O32" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -15047,7 +14657,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03583571-B224-0645-BF80-2ED912E75027}">
-  <dimension ref="A1:O33"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20" style="4" customWidth="1"/>
@@ -15900,389 +15510,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A25" s="7" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A26" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="H26" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="I26" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="J26" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="K26" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="L26" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="M26" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="N26" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="O26" s="4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A27" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="I27" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J27" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="K27" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="L27" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="M27" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="N27" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="O27" s="4" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A28" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="H28" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="I28" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="J28" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="K28" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="L28" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="M28" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="N28" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="O28" s="4" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A29" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="H29" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="I29" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J29" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="K29" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="L29" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="M29" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="N29" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="O29" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A30" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="I30" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="J30" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="K30" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="L30" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="M30" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="N30" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="O30" s="4" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A31" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H31" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="I31" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="J31" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="K31" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="L31" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="M31" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="N31" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="O31" s="4" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A32" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="H32" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="I32" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="J32" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="K32" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="L32" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="M32" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="N32" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="O32" s="4" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A33" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H33" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="I33" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="J33" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="K33" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="L33" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="M33" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="N33" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="O33" s="4" t="s">
-        <v>192</v>
-      </c>
-    </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/NBA_Finals_Spurs_Knicks_Stats.xlsx
+++ b/NBA_Finals_Spurs_Knicks_Stats.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adamkaribian/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adamkaribian/Downloads/files/nba-finals-dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EC7EA9C-BCDB-DE44-B5B4-5437B52043B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C3D26DC6-6D88-3D40-B786-826588DE4B48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="620" windowWidth="28040" windowHeight="16080" activeTab="7" xr2:uid="{7BDB8F1F-88A5-804B-B69B-31264D15A624}"/>
+    <workbookView xWindow="340" yWindow="620" windowWidth="28040" windowHeight="16080" activeTab="7" xr2:uid="{7BDB8F1F-88A5-804B-B69B-31264D15A624}"/>
   </bookViews>
   <sheets>
     <sheet name="Knicks R1" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4496" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4738" uniqueCount="266">
   <si>
     <t>Player</t>
   </si>
@@ -835,6 +835,15 @@
   </si>
   <si>
     <t>11-21</t>
+  </si>
+  <si>
+    <t>11-25</t>
+  </si>
+  <si>
+    <t>11-18</t>
+  </si>
+  <si>
+    <t>5-18</t>
   </si>
 </sst>
 </file>
@@ -13797,7 +13806,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F1BDEF0-D7A0-B141-9ABB-88CC0DA9304B}">
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:O32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.5" style="4" customWidth="1"/>
@@ -14650,6 +14659,387 @@
         <v>76</v>
       </c>
     </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A24" s="7" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A25" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K25" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L25" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="M25" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="N25" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="O25" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A26" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="K26" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L26" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M26" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="N26" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="O26" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A27" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K27" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="L27" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M27" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="N27" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="O27" s="4" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A28" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K28" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L28" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="M28" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="N28" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="O28" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A29" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K29" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="L29" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M29" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="N29" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="O29" s="4" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A30" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J30" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K30" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="L30" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="M30" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="N30" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="O30" s="4" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A31" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J31" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K31" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L31" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M31" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="N31" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="O31" s="4" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A32" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J32" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K32" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="L32" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="M32" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="N32" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="O32" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -14657,7 +15047,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03583571-B224-0645-BF80-2ED912E75027}">
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:O33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20" style="4" customWidth="1"/>
@@ -15510,7 +15900,389 @@
         <v>213</v>
       </c>
     </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A25" s="7" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A26" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="K26" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="L26" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="M26" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="N26" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="O26" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A27" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K27" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="L27" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M27" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="N27" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="O27" s="4" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A28" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="K28" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L28" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="M28" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="N28" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="O28" s="4" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A29" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K29" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="L29" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="M29" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="N29" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="O29" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A30" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J30" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="K30" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L30" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M30" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="N30" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="O30" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A31" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J31" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="K31" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="L31" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="M31" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="N31" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="O31" s="4" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A32" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J32" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K32" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="L32" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M32" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="N32" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="O32" s="4" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A33" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="K33" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="L33" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M33" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="N33" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="O33" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>